--- a/data/trans_orig/P1432-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1432-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de incontinencia urinaria en 2007</t>
+          <t>Población con diagnóstico de incontinencia urinaria en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16631</t>
+          <t>16552</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36279</t>
+          <t>35592</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30963</t>
+          <t>30253</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56814</t>
+          <t>57204</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52579</t>
+          <t>52618</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84906</t>
+          <t>86374</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>995444</t>
+          <t>996131</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1015092</t>
+          <t>1015171</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1258299</t>
+          <t>1257909</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1284150</t>
+          <t>1284860</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2261929</t>
+          <t>2260461</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2294256</t>
+          <t>2294217</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2669</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12230</t>
+          <t>11488</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>3852</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16566</t>
+          <t>15485</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,47 +1125,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>14545</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>8149</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>23141</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>14545</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>8493</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>23485</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1681183</t>
+          <t>1681925</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1690744</t>
+          <t>1690899</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1571107</t>
+          <t>1572188</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1583759</t>
+          <t>1583821</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,47 +1238,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>99,76%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>3188</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>3266541</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>3257945</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3272937</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>99,29%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>99,75%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>3188</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>3266541</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>3257601</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3272593</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>99,28%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12068</t>
+          <t>12052</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11741</t>
+          <t>11743</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>539340</t>
+          <t>539356</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>550343</t>
+          <t>550390</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>474393</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>476412</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1016079</t>
+          <t>1016077</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1026767</t>
+          <t>1026763</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26042</t>
+          <t>26480</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48980</t>
+          <t>49392</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37704</t>
+          <t>38308</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65998</t>
+          <t>68044</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70998</t>
+          <t>68992</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106205</t>
+          <t>106354</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3227563</t>
+          <t>3227151</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3250501</t>
+          <t>3250063</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3313199</t>
+          <t>3311153</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3341493</t>
+          <t>3340889</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6549536</t>
+          <t>6549387</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6584743</t>
+          <t>6586749</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de incontinencia urinaria en 2012</t>
+          <t>Población con diagnóstico de incontinencia urinaria en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7820</t>
+          <t>8007</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23846</t>
+          <t>24944</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35078</t>
+          <t>36606</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64154</t>
+          <t>65369</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48578</t>
+          <t>47523</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80496</t>
+          <t>80952</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>950797</t>
+          <t>949699</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>966823</t>
+          <t>966636</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1272534</t>
+          <t>1271319</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1301610</t>
+          <t>1300082</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2230835</t>
+          <t>2230379</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2262753</t>
+          <t>2263808</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3399</t>
+          <t>4145</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18597</t>
+          <t>18401</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13138</t>
+          <t>13033</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>7897</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25363</t>
+          <t>25665</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1945360</t>
+          <t>1945556</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1960558</t>
+          <t>1959812</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1741454</t>
+          <t>1741559</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1752266</t>
+          <t>1752454</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3693186</t>
+          <t>3692884</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3710262</t>
+          <t>3710652</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>981</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8754</t>
+          <t>9487</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>976</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8345</t>
+          <t>9170</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>479077</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>481181</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>449877</t>
+          <t>449144</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>457661</t>
+          <t>457650</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>931468</t>
+          <t>930643</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>938836</t>
+          <t>938837</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14561</t>
+          <t>14646</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37374</t>
+          <t>36519</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43524</t>
+          <t>42621</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75296</t>
+          <t>76667</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>64488</t>
+          <t>64181</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>102794</t>
+          <t>99892</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3382408</t>
+          <t>3383263</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3405221</t>
+          <t>3405136</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3474615</t>
+          <t>3473244</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3506387</t>
+          <t>3507290</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6866899</t>
+          <t>6869801</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6905205</t>
+          <t>6905512</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de incontinencia urinaria en 2016</t>
+          <t>Población con diagnóstico de incontinencia urinaria en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6254</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19208</t>
+          <t>19909</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22234</t>
+          <t>23406</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47202</t>
+          <t>48795</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33362</t>
+          <t>32954</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60729</t>
+          <t>60141</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>735139</t>
+          <t>734438</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>748093</t>
+          <t>747429</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>947458</t>
+          <t>945865</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>972426</t>
+          <t>971254</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1688278</t>
+          <t>1688866</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1715645</t>
+          <t>1716053</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1719</t>
+          <t>1690</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10025</t>
+          <t>10418</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8711</t>
+          <t>9158</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25303</t>
+          <t>25022</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11583</t>
+          <t>12203</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30785</t>
+          <t>30603</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2066360</t>
+          <t>2065967</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2074666</t>
+          <t>2074695</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1962997</t>
+          <t>1963278</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1979589</t>
+          <t>1979142</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4033900</t>
+          <t>4034082</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4053102</t>
+          <t>4052482</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8601</t>
+          <t>8173</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>889</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9926</t>
+          <t>8405</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>542331</t>
+          <t>542341</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>540539</t>
+          <t>540967</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1086101</t>
+          <t>1087622</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1095128</t>
+          <t>1095138</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11118</t>
+          <t>11057</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26588</t>
+          <t>26907</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37274</t>
+          <t>37860</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69057</t>
+          <t>68749</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52983</t>
+          <t>53577</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86212</t>
+          <t>88753</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3351030</t>
+          <t>3350711</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3366500</t>
+          <t>3366561</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3463043</t>
+          <t>3463351</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3494826</t>
+          <t>3494240</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6823506</t>
+          <t>6820965</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6856735</t>
+          <t>6856141</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1432-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1432-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16552</t>
+          <t>16504</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35592</t>
+          <t>35397</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30253</t>
+          <t>31383</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57204</t>
+          <t>57229</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52618</t>
+          <t>51760</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86374</t>
+          <t>84690</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>996131</t>
+          <t>996326</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1015171</t>
+          <t>1015219</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1257909</t>
+          <t>1257884</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1284860</t>
+          <t>1283730</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2260461</t>
+          <t>2262145</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2294217</t>
+          <t>2295075</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2514</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11488</t>
+          <t>12251</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15485</t>
+          <t>16459</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8149</t>
+          <t>8724</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23141</t>
+          <t>23205</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1681925</t>
+          <t>1681162</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1690899</t>
+          <t>1690811</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1572188</t>
+          <t>1571214</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1583821</t>
+          <t>1583775</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3257945</t>
+          <t>3257881</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3272937</t>
+          <t>3272362</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12052</t>
+          <t>12333</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11743</t>
+          <t>11344</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>539356</t>
+          <t>539075</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>550390</t>
+          <t>549782</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1016077</t>
+          <t>1016476</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1026763</t>
+          <t>1026810</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26480</t>
+          <t>26081</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49392</t>
+          <t>49788</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38308</t>
+          <t>37609</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68044</t>
+          <t>66395</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68992</t>
+          <t>68472</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106354</t>
+          <t>106966</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3227151</t>
+          <t>3226755</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3250063</t>
+          <t>3250462</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3311153</t>
+          <t>3312802</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3340889</t>
+          <t>3341588</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6549387</t>
+          <t>6548775</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6586749</t>
+          <t>6587269</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8007</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24944</t>
+          <t>25015</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36606</t>
+          <t>35452</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65369</t>
+          <t>65134</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47523</t>
+          <t>46928</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80952</t>
+          <t>80513</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>949699</t>
+          <t>949628</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>966636</t>
+          <t>966591</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1271319</t>
+          <t>1271554</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1300082</t>
+          <t>1301236</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2230379</t>
+          <t>2230818</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2263808</t>
+          <t>2264403</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18401</t>
+          <t>19612</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13033</t>
+          <t>13147</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>8535</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25665</t>
+          <t>25065</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1945556</t>
+          <t>1944345</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1959812</t>
+          <t>1960789</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1741559</t>
+          <t>1741445</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1752454</t>
+          <t>1751738</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3692884</t>
+          <t>3693484</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3710652</t>
+          <t>3710014</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>974</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>973</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9170</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>449144</t>
+          <t>449404</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>457650</t>
+          <t>457657</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>930643</t>
+          <t>931332</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>938837</t>
+          <t>938840</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14646</t>
+          <t>13923</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36519</t>
+          <t>35122</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42621</t>
+          <t>43279</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76667</t>
+          <t>74767</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>64181</t>
+          <t>62086</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>99892</t>
+          <t>98397</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3383263</t>
+          <t>3384660</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3405136</t>
+          <t>3405859</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3473244</t>
+          <t>3475144</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3507290</t>
+          <t>3506632</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6869801</t>
+          <t>6871296</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6905512</t>
+          <t>6907607</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6918</t>
+          <t>6826</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19909</t>
+          <t>20113</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23406</t>
+          <t>22764</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48795</t>
+          <t>47859</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32954</t>
+          <t>33570</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60141</t>
+          <t>61997</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>734438</t>
+          <t>734234</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>747429</t>
+          <t>747521</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>945865</t>
+          <t>946801</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>971254</t>
+          <t>971896</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1688866</t>
+          <t>1687010</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1716053</t>
+          <t>1715437</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1690</t>
+          <t>1705</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10418</t>
+          <t>10375</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9158</t>
+          <t>8855</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25022</t>
+          <t>24361</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12203</t>
+          <t>11424</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30603</t>
+          <t>30376</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2065967</t>
+          <t>2066010</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2074695</t>
+          <t>2074680</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1963278</t>
+          <t>1963939</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1979142</t>
+          <t>1979445</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4034082</t>
+          <t>4034309</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4052482</t>
+          <t>4053261</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4545</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8173</t>
+          <t>8773</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>898</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8405</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>542341</t>
+          <t>541652</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>540967</t>
+          <t>540367</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1087622</t>
+          <t>1086408</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1095138</t>
+          <t>1095129</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11057</t>
+          <t>11580</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26907</t>
+          <t>26244</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37860</t>
+          <t>36674</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68749</t>
+          <t>66829</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53577</t>
+          <t>53087</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88753</t>
+          <t>86737</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3350711</t>
+          <t>3351374</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3366561</t>
+          <t>3366038</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3463351</t>
+          <t>3465271</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3494240</t>
+          <t>3495426</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6820965</t>
+          <t>6822981</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6856141</t>
+          <t>6856631</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
